--- a/WorkBot/refactor/data/orders/US Foods/CompletedOrders/US Foods_Collegetown_2025-10-08.xlsx
+++ b/WorkBot/refactor/data/orders/US Foods/CompletedOrders/US Foods_Collegetown_2025-10-08.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,6 +551,438 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2945517</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PKT Sugar - Splenda (Yellow)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>30.83</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>30.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5614176</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bread - GF</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>43.49</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>86.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7698844</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Whipped Cream</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>52.32</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>52.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8600421</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dirty Chip - Jalapeno Hot (2oz)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>17.90</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>17.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1438993</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dirty Chip - Mesquite Barbecue (2oz)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>17.90</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>17.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2559979</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dirty Chip - Salt &amp; Vinegar (2oz)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>17.90</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>17.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>8495343</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dirty Chip - Sour Cream &amp; Onion (2oz)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>18.00</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>36.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1030194</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Bleach</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>13.10</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>13.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1365278</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Vegan Chicken Tenders</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>87.80</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>175.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2825368</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sausage - Chicken Patty</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>50.98</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>152.94</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3357597</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>FRZ Fruit - Strawberry (Whole)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>43.74</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>131.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>6457558</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>FRZ Banana - Slices</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>21.78</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>43.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1027038</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ice Cream - Vanilla (3 Gal)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>26.30</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>26.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1027035</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ice Cream - Chocolate (3 Gal)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>26.30</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>26.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1667864</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Employee Water</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>7.81</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>93.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>4858587</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Hals - Original</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>17.80</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>17.80</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
